--- a/AtchisonRegime/Outputs/USA/USA_Low_Volatility/df_regEquityReturns_USA_Low_Volatility.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Low_Volatility/df_regEquityReturns_USA_Low_Volatility.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q130"/>
+  <dimension ref="A1:Q131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7255,7 +7255,7 @@
         <v>-1.113652454430497</v>
       </c>
       <c r="C120" t="n">
-        <v>0.006266379198084816</v>
+        <v>-0.01570867082860625</v>
       </c>
       <c r="D120" t="b">
         <v>0</v>
@@ -7312,7 +7312,7 @@
         <v>-1.13653593688915</v>
       </c>
       <c r="C121" t="n">
-        <v>0.02240605369896704</v>
+        <v>0.005131485533573125</v>
       </c>
       <c r="D121" t="b">
         <v>0</v>
@@ -7369,7 +7369,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="C122" t="n">
-        <v>0.05890779434252914</v>
+        <v>0.04460226520446691</v>
       </c>
       <c r="D122" t="b">
         <v>0</v>
@@ -7426,7 +7426,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1365357185829741</v>
+        <v>0.10691331821946</v>
       </c>
       <c r="D123" t="b">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C124" t="n">
-        <v>0.19626538484902</v>
+        <v>0.1742576329953394</v>
       </c>
       <c r="D124" t="b">
         <v>0</v>
@@ -7540,7 +7540,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C125" t="n">
-        <v>0.2479141243562677</v>
+        <v>0.2230893786343014</v>
       </c>
       <c r="D125" t="b">
         <v>0</v>
@@ -7597,7 +7597,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C126" t="n">
-        <v>0.2597235153389927</v>
+        <v>0.2419933628466199</v>
       </c>
       <c r="D126" t="b">
         <v>0</v>
@@ -7654,7 +7654,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C127" t="n">
-        <v>0.2098083315261438</v>
+        <v>0.2090047006632499</v>
       </c>
       <c r="D127" t="b">
         <v>0</v>
@@ -7711,7 +7711,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1536160686024298</v>
+        <v>0.1277646818410845</v>
       </c>
       <c r="D128" t="b">
         <v>0</v>
@@ -7765,10 +7765,10 @@
         <v>45716</v>
       </c>
       <c r="B129" t="n">
-        <v>-0.8167702922088305</v>
+        <v>-0.8165764810113098</v>
       </c>
       <c r="C129" t="n">
-        <v>0.04657800836005581</v>
+        <v>0.03018097094312175</v>
       </c>
       <c r="D129" t="b">
         <v>0</v>
@@ -7822,10 +7822,10 @@
         <v>45747</v>
       </c>
       <c r="B130" t="n">
-        <v>-0.7844280456827043</v>
+        <v>-0.836774216411349</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>-0.04969816765883398</v>
       </c>
       <c r="D130" t="b">
         <v>0</v>
@@ -7871,6 +7871,63 @@
         <v>142.8472018973754</v>
       </c>
       <c r="Q130" t="n">
+        <v>129.9158523273247</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B131" t="n">
+        <v>-0.879407738343786</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.07980487945422567</v>
+      </c>
+      <c r="D131" t="b">
+        <v>0</v>
+      </c>
+      <c r="E131" t="b">
+        <v>1</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-8.555517241595799</v>
+      </c>
+      <c r="G131" t="n">
+        <v>487160.1553182143</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>-8.555517241595799</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>154.641457735588</v>
+      </c>
+      <c r="O131" t="n">
+        <v>166.8240563423862</v>
+      </c>
+      <c r="P131" t="n">
+        <v>142.8472018973754</v>
+      </c>
+      <c r="Q131" t="n">
         <v>129.9158523273247</v>
       </c>
     </row>
